--- a/DA418_S1_Progress Tracker.xlsx
+++ b/DA418_S1_Progress Tracker.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Anitha\NIIT\Capstone Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Anitha\NIIT\Capstone Project\capstone-project-retail-tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AA9E9E0-A73D-481F-A716-1C8E93E43FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A4BE77-1B79-4E01-87DF-2DBA804AE331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{EE05F723-CC45-4365-ABE9-4CF4A7CBB336}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{EE05F723-CC45-4365-ABE9-4CF4A7CBB336}"/>
   </bookViews>
   <sheets>
     <sheet name="Phase 1" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="90">
   <si>
     <t>Capstone Project - Phase 1 End Tracker</t>
   </si>
@@ -297,53 +297,71 @@
     <t>Rehearsal &amp; Delivery Readiness</t>
   </si>
   <si>
-    <t>Documentation Started</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>N/a</t>
-  </si>
-  <si>
-    <t>Mentor Review</t>
-  </si>
-  <si>
     <t>E-Commerce Customer Analytics: Sales, Conversion, Retension and Churn Prediction</t>
   </si>
   <si>
     <t>DA764S76</t>
   </si>
   <si>
-    <t>Explore, Clean and Process, Store Clean Data, Git Repo Setup and Draft Hypothesis</t>
-  </si>
-  <si>
-    <t>Document in Progress</t>
-  </si>
-  <si>
-    <t>In Progress</t>
-  </si>
-  <si>
-    <t>to download ad review</t>
-  </si>
-  <si>
     <t>18=08-2026</t>
   </si>
   <si>
     <t>Close the deadline</t>
   </si>
   <si>
-    <t>Created Report - Yes Explored Data</t>
-  </si>
-  <si>
     <t>Not Started</t>
+  </si>
+  <si>
+    <t>Anitha R</t>
+  </si>
+  <si>
+    <t>Customer Dataset</t>
+  </si>
+  <si>
+    <t>Geolocaion Dataset</t>
+  </si>
+  <si>
+    <t>Order Items Dataset</t>
+  </si>
+  <si>
+    <t>Order Reviews Dataset</t>
+  </si>
+  <si>
+    <t>Orders Dataset</t>
+  </si>
+  <si>
+    <t>Products Dataset</t>
+  </si>
+  <si>
+    <t>Excel</t>
+  </si>
+  <si>
+    <t>to download and review</t>
+  </si>
+  <si>
+    <t>https://myrepos.stackroute.niit.com/1943693_Anitha/capstone-project-retail-tech</t>
+  </si>
+  <si>
+    <t>Created Report - Yes Explored Datasets</t>
+  </si>
+  <si>
+    <t>Prep Data</t>
+  </si>
+  <si>
+    <t>Complete it by 24-08-2026</t>
+  </si>
+  <si>
+    <t>Create Git Repository</t>
+  </si>
+  <si>
+    <t>Individual Project</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -424,6 +442,20 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -587,10 +619,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -665,7 +698,32 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -680,7 +738,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -689,23 +756,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -716,24 +768,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1618,19 +1664,19 @@
     <col min="4" max="4" width="21.140625" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
     <col min="6" max="6" width="24.7109375" customWidth="1"/>
-    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="7" max="7" width="25" customWidth="1"/>
     <col min="8" max="8" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="28.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="32"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="41"/>
     </row>
     <row r="2" spans="2:8" ht="26.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
@@ -1641,28 +1687,32 @@
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="34"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="43"/>
     </row>
     <row r="3" spans="2:8" ht="26.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="46"/>
+      <c r="C3" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="53"/>
     </row>
     <row r="4" spans="2:8" ht="37.5" x14ac:dyDescent="0.3">
       <c r="B4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="41"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="43"/>
+      <c r="C4" s="44" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="46"/>
     </row>
     <row r="5" spans="2:8" ht="37.5" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
@@ -1678,39 +1728,45 @@
       <c r="B6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="35"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="37"/>
+      <c r="C6" s="54" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="49"/>
     </row>
     <row r="7" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="35"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="37"/>
+      <c r="C7" s="55" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="49"/>
     </row>
     <row r="8" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="35"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="37"/>
+      <c r="C8" s="47">
+        <v>46252</v>
+      </c>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="49"/>
     </row>
     <row r="9" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B9" s="38"/>
-      <c r="C9" s="39"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="40"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="39"/>
     </row>
     <row r="10" spans="2:8" s="1" customFormat="1" ht="52.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
@@ -1739,75 +1795,139 @@
       <c r="B11" s="5">
         <v>1</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
+      <c r="C11" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>82</v>
+      </c>
       <c r="E11" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="5">
         <v>2</v>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
+      <c r="C12" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" s="5">
         <v>3</v>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
+      <c r="C13" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" s="5">
         <v>4</v>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
+      <c r="C14" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="5">
         <v>5</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
+      <c r="C15" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="5">
         <v>6</v>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
+      <c r="C16" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="5">
@@ -1864,6 +1984,7 @@
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
   </mergeCells>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -1885,13 +2006,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="24" x14ac:dyDescent="0.4">
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="50" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="32"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="41"/>
     </row>
     <row r="2" spans="2:9" ht="37.5" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
@@ -1901,44 +2022,44 @@
         <v>2</v>
       </c>
       <c r="D2" s="2"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="34"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="43"/>
     </row>
     <row r="3" spans="2:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="37"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="49"/>
     </row>
     <row r="4" spans="2:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="35"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="37"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="49"/>
     </row>
     <row r="5" spans="2:9" ht="56.25" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="37"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="49"/>
     </row>
     <row r="6" spans="2:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="35"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="37"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="49"/>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25"/>
     <row r="8" spans="2:9" s="9" customFormat="1" ht="144" x14ac:dyDescent="0.25">
@@ -2125,14 +2246,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="24" x14ac:dyDescent="0.4">
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="32"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="41"/>
       <c r="H1" s="9"/>
     </row>
     <row r="2" spans="2:11" ht="56.25" x14ac:dyDescent="0.3">
@@ -2144,69 +2265,67 @@
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="34"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="43"/>
       <c r="H2" s="9"/>
     </row>
     <row r="3" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="51" t="s">
-        <v>75</v>
-      </c>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="37"/>
+      <c r="C3" s="55" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="49"/>
       <c r="H3" s="10"/>
     </row>
     <row r="4" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="35"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="37"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="49"/>
       <c r="H4" s="10"/>
     </row>
     <row r="5" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="37"/>
+      <c r="C5" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="49"/>
       <c r="H5" s="10"/>
     </row>
     <row r="6" spans="2:11" ht="56.25" x14ac:dyDescent="0.3">
       <c r="B6" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="35"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="37"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="49"/>
       <c r="H6" s="10"/>
     </row>
     <row r="7" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="50">
-        <v>46252</v>
-      </c>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="37"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="49"/>
       <c r="H7" s="10"/>
     </row>
     <row r="9" spans="2:11" s="28" customFormat="1" ht="90" x14ac:dyDescent="0.25">
@@ -2245,56 +2364,26 @@
       <c r="B10" s="5">
         <v>1</v>
       </c>
-      <c r="C10" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="G10" s="52" t="s">
-        <v>77</v>
-      </c>
-      <c r="H10" s="29">
-        <v>46265</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>73</v>
-      </c>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" s="5">
         <v>2</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="H11" s="29">
-        <v>46258</v>
-      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="29"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -2548,18 +2637,19 @@
     <col min="4" max="4" width="25.5703125" customWidth="1"/>
     <col min="5" max="5" width="18.7109375" customWidth="1"/>
     <col min="6" max="7" width="19.28515625" customWidth="1"/>
-    <col min="8" max="8" width="15.5703125" customWidth="1"/>
-    <col min="9" max="10" width="17.140625" customWidth="1"/>
+    <col min="8" max="8" width="24.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.85546875" customWidth="1"/>
+    <col min="10" max="10" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="24" x14ac:dyDescent="0.4">
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
     </row>
     <row r="2" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="25" t="s">
@@ -2569,43 +2659,51 @@
         <v>2</v>
       </c>
       <c r="D2" s="25"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
     </row>
     <row r="3" spans="2:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B3" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
+      <c r="C3" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
       <c r="F3" s="27"/>
     </row>
     <row r="4" spans="2:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B4" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
+      <c r="C4" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
       <c r="F4" s="27"/>
     </row>
     <row r="5" spans="2:9" ht="31.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
+      <c r="C5" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
       <c r="F5" s="27"/>
     </row>
     <row r="6" spans="2:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B6" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
+      <c r="C6" s="34">
+        <v>46254</v>
+      </c>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
       <c r="F6" s="27"/>
     </row>
     <row r="8" spans="2:9" ht="90" x14ac:dyDescent="0.25">
@@ -2639,18 +2737,24 @@
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E9" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>86</v>
+      </c>
       <c r="F9" s="29">
         <v>46258</v>
       </c>
       <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
+      <c r="H9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B10" s="5">
@@ -2769,8 +2873,11 @@
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="E1:F2"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{45F67C93-BCE7-4B12-912B-7DA2A674501F}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2792,16 +2899,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="24" x14ac:dyDescent="0.4">
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="32"/>
-    </row>
-    <row r="2" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="41"/>
+    </row>
+    <row r="2" spans="2:11" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
@@ -2810,48 +2917,56 @@
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="34"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="43"/>
     </row>
     <row r="3" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="37"/>
+      <c r="C3" s="55" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="49"/>
     </row>
     <row r="4" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="35"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="37"/>
+      <c r="C4" s="55" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="49"/>
     </row>
     <row r="5" spans="2:11" ht="56.25" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="37"/>
+      <c r="C5" s="56" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="49"/>
     </row>
     <row r="6" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="35"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="37"/>
+      <c r="C6" s="47">
+        <v>46255</v>
+      </c>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="49"/>
     </row>
     <row r="8" spans="2:11" ht="90" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
@@ -3034,8 +3149,11 @@
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="C5:G5"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{5B36C8BE-AA62-49F2-B0AF-9F7EA464A93D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -3057,14 +3175,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="24" x14ac:dyDescent="0.4">
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="50" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="32"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="41"/>
     </row>
     <row r="2" spans="2:11" ht="56.25" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
@@ -3075,48 +3193,48 @@
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="34"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="43"/>
     </row>
     <row r="3" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="37"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="49"/>
     </row>
     <row r="4" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="35"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="37"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="49"/>
     </row>
     <row r="5" spans="2:11" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="37"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="49"/>
     </row>
     <row r="6" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="35"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="37"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="49"/>
     </row>
     <row r="8" spans="2:11" ht="90" x14ac:dyDescent="0.25">
       <c r="B8" s="15" t="s">
@@ -3322,14 +3440,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="24" x14ac:dyDescent="0.4">
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="32"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="41"/>
     </row>
     <row r="2" spans="2:11" ht="56.25" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
@@ -3340,48 +3458,48 @@
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="34"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="43"/>
     </row>
     <row r="3" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="37"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="49"/>
     </row>
     <row r="4" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="35"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="37"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="49"/>
     </row>
     <row r="5" spans="2:11" ht="56.25" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="37"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="49"/>
     </row>
     <row r="6" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="35"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="37"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="49"/>
     </row>
     <row r="8" spans="2:11" ht="90" x14ac:dyDescent="0.25">
       <c r="B8" s="15" t="s">
@@ -3585,13 +3703,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="24" x14ac:dyDescent="0.4">
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="31"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="40"/>
     </row>
     <row r="2" spans="2:9" ht="37.5" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
@@ -3602,43 +3720,43 @@
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="33"/>
+      <c r="F2" s="42"/>
     </row>
     <row r="3" spans="2:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
     </row>
     <row r="4" spans="2:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="35"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
     </row>
     <row r="5" spans="2:9" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
     </row>
     <row r="6" spans="2:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="35"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
     </row>
     <row r="8" spans="2:9" ht="56.25" x14ac:dyDescent="0.25">
       <c r="B8" s="15" t="s">
@@ -3949,15 +4067,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="24" x14ac:dyDescent="0.4">
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="50" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="32"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="41"/>
     </row>
     <row r="2" spans="2:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
@@ -3969,52 +4087,52 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="34"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="43"/>
     </row>
     <row r="3" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="37"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="49"/>
     </row>
     <row r="4" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="35"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="37"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="49"/>
     </row>
     <row r="5" spans="2:11" ht="37.5" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="37"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="49"/>
     </row>
     <row r="6" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="35"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="37"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="49"/>
     </row>
     <row r="8" spans="2:11" s="1" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="B8" s="17" t="s">
@@ -4220,15 +4338,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="24" x14ac:dyDescent="0.4">
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="32"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="41"/>
     </row>
     <row r="2" spans="2:10" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
@@ -4240,52 +4358,52 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="34"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="43"/>
     </row>
     <row r="3" spans="2:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="37"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="49"/>
     </row>
     <row r="4" spans="2:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="35"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="37"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="49"/>
     </row>
     <row r="5" spans="2:10" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="37"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="49"/>
     </row>
     <row r="6" spans="2:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="35"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="37"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="49"/>
     </row>
     <row r="8" spans="2:10" ht="90" x14ac:dyDescent="0.25">
       <c r="B8" s="15" t="s">
@@ -4477,14 +4595,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="24" x14ac:dyDescent="0.4">
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="32"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="41"/>
     </row>
     <row r="2" spans="2:10" ht="56.25" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
@@ -4495,48 +4613,48 @@
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="34"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="43"/>
     </row>
     <row r="3" spans="2:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="37"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="49"/>
     </row>
     <row r="4" spans="2:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="35"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="37"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="49"/>
     </row>
     <row r="5" spans="2:10" ht="56.25" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="37"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="49"/>
     </row>
     <row r="6" spans="2:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="35"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="37"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="49"/>
     </row>
     <row r="8" spans="2:10" s="9" customFormat="1" ht="162" x14ac:dyDescent="0.25">
       <c r="B8" s="15" t="s">
@@ -4712,6 +4830,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b18f8198-02fb-408b-a649-baf04150ea28">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0f01b7b4-d4b6-47da-93c5-cffa90a406b9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D80C9320661FCB478F077E19A50F7652" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8169698a23ce641b0e514e4179e9fb48">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0f01b7b4-d4b6-47da-93c5-cffa90a406b9" xmlns:ns3="b18f8198-02fb-408b-a649-baf04150ea28" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2c955a956371819644e2cb74c9337ca9" ns2:_="" ns3:_="">
     <xsd:import namespace="0f01b7b4-d4b6-47da-93c5-cffa90a406b9"/>
@@ -4960,27 +5098,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E88113A-166D-44CD-886E-1102874B4258}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b18f8198-02fb-408b-a649-baf04150ea28">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="0f01b7b4-d4b6-47da-93c5-cffa90a406b9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E8D7F3F-2EC6-459C-B8E1-5F91591B843B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b18f8198-02fb-408b-a649-baf04150ea28"/>
+    <ds:schemaRef ds:uri="0f01b7b4-d4b6-47da-93c5-cffa90a406b9"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F5E3A78-D3D4-4E16-B9AF-E3B8ACF9F7D8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4997,23 +5134,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E88113A-166D-44CD-886E-1102874B4258}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E8D7F3F-2EC6-459C-B8E1-5F91591B843B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b18f8198-02fb-408b-a649-baf04150ea28"/>
-    <ds:schemaRef ds:uri="0f01b7b4-d4b6-47da-93c5-cffa90a406b9"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/DA418_S1_Progress Tracker.xlsx
+++ b/DA418_S1_Progress Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Anitha\NIIT\Capstone Project\capstone-project-retail-tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A4BE77-1B79-4E01-87DF-2DBA804AE331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{477C6AF9-3233-4EF4-B3D7-9EDDCBCC6C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{EE05F723-CC45-4365-ABE9-4CF4A7CBB336}"/>
   </bookViews>
@@ -699,6 +699,66 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -716,66 +776,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1669,14 +1669,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="28.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="41"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="33"/>
     </row>
     <row r="2" spans="2:8" ht="26.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
@@ -1687,20 +1687,20 @@
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="43"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="35"/>
     </row>
     <row r="3" spans="2:8" ht="26.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="51" t="s">
+      <c r="C3" s="47" t="s">
         <v>71</v>
       </c>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="53"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="49"/>
     </row>
     <row r="4" spans="2:8" ht="37.5" x14ac:dyDescent="0.3">
       <c r="B4" s="11" t="s">
@@ -1728,45 +1728,45 @@
       <c r="B6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="54" t="s">
+      <c r="C6" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="49"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="38"/>
     </row>
     <row r="7" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="55" t="s">
+      <c r="C7" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="49"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="38"/>
     </row>
     <row r="8" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="47">
+      <c r="C8" s="39">
         <v>46252</v>
       </c>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="49"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="38"/>
     </row>
     <row r="9" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B9" s="37"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="39"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="43"/>
     </row>
     <row r="10" spans="2:8" s="1" customFormat="1" ht="52.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
@@ -2006,13 +2006,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="24" x14ac:dyDescent="0.4">
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="41"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="33"/>
     </row>
     <row r="2" spans="2:9" ht="37.5" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
@@ -2022,44 +2022,44 @@
         <v>2</v>
       </c>
       <c r="D2" s="2"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="43"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="35"/>
     </row>
     <row r="3" spans="2:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="49"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="38"/>
     </row>
     <row r="4" spans="2:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="49"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="38"/>
     </row>
     <row r="5" spans="2:9" ht="56.25" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="54"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="49"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="38"/>
     </row>
     <row r="6" spans="2:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="54"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="49"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="38"/>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25"/>
     <row r="8" spans="2:9" s="9" customFormat="1" ht="144" x14ac:dyDescent="0.25">
@@ -2246,14 +2246,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="24" x14ac:dyDescent="0.4">
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="41"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="33"/>
       <c r="H1" s="9"/>
     </row>
     <row r="2" spans="2:11" ht="56.25" x14ac:dyDescent="0.3">
@@ -2265,67 +2265,67 @@
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="43"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="35"/>
       <c r="H2" s="9"/>
     </row>
     <row r="3" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="55" t="s">
+      <c r="C3" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="49"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="38"/>
       <c r="H3" s="10"/>
     </row>
     <row r="4" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="49"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="38"/>
       <c r="H4" s="10"/>
     </row>
     <row r="5" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="54" t="s">
+      <c r="C5" s="50" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="49"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="38"/>
       <c r="H5" s="10"/>
     </row>
     <row r="6" spans="2:11" ht="56.25" x14ac:dyDescent="0.3">
       <c r="B6" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="54"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="49"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="38"/>
       <c r="H6" s="10"/>
     </row>
     <row r="7" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="47"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="49"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="38"/>
       <c r="H7" s="10"/>
     </row>
     <row r="9" spans="2:11" s="28" customFormat="1" ht="90" x14ac:dyDescent="0.25">
@@ -2643,13 +2643,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="24" x14ac:dyDescent="0.4">
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
     </row>
     <row r="2" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="25" t="s">
@@ -2659,51 +2659,51 @@
         <v>2</v>
       </c>
       <c r="D2" s="25"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
     </row>
     <row r="3" spans="2:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B3" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="52" t="s">
         <v>71</v>
       </c>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
       <c r="F3" s="27"/>
     </row>
     <row r="4" spans="2:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B4" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
       <c r="F4" s="27"/>
     </row>
     <row r="5" spans="2:9" ht="31.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="35" t="s">
+      <c r="C5" s="55" t="s">
         <v>84</v>
       </c>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
       <c r="F5" s="27"/>
     </row>
     <row r="6" spans="2:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B6" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="34">
+      <c r="C6" s="54">
         <v>46254</v>
       </c>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
       <c r="F6" s="27"/>
     </row>
     <row r="8" spans="2:9" ht="90" x14ac:dyDescent="0.25">
@@ -2748,7 +2748,9 @@
       <c r="F9" s="29">
         <v>46258</v>
       </c>
-      <c r="G9" s="2"/>
+      <c r="G9" s="29">
+        <v>46256</v>
+      </c>
       <c r="H9" s="2" t="s">
         <v>87</v>
       </c>
@@ -2899,14 +2901,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="24" x14ac:dyDescent="0.4">
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="41"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="33"/>
     </row>
     <row r="2" spans="2:11" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
@@ -2917,56 +2919,56 @@
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="43"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="35"/>
     </row>
     <row r="3" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="55" t="s">
+      <c r="C3" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="49"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="38"/>
     </row>
     <row r="4" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="55" t="s">
+      <c r="C4" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="49"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="38"/>
     </row>
     <row r="5" spans="2:11" ht="56.25" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="56" t="s">
+      <c r="C5" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="49"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="38"/>
     </row>
     <row r="6" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="47">
+      <c r="C6" s="39">
         <v>46255</v>
       </c>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="49"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="38"/>
     </row>
     <row r="8" spans="2:11" ht="90" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
@@ -3175,14 +3177,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="24" x14ac:dyDescent="0.4">
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="41"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="33"/>
     </row>
     <row r="2" spans="2:11" ht="56.25" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
@@ -3193,48 +3195,48 @@
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="43"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="35"/>
     </row>
     <row r="3" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="49"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="38"/>
     </row>
     <row r="4" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="49"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="38"/>
     </row>
     <row r="5" spans="2:11" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="54"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="49"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="38"/>
     </row>
     <row r="6" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="54"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="49"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="38"/>
     </row>
     <row r="8" spans="2:11" ht="90" x14ac:dyDescent="0.25">
       <c r="B8" s="15" t="s">
@@ -3440,14 +3442,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="24" x14ac:dyDescent="0.4">
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="41"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="33"/>
     </row>
     <row r="2" spans="2:11" ht="56.25" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
@@ -3458,48 +3460,48 @@
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="43"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="35"/>
     </row>
     <row r="3" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="49"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="38"/>
     </row>
     <row r="4" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="49"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="38"/>
     </row>
     <row r="5" spans="2:11" ht="56.25" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="54"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="49"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="38"/>
     </row>
     <row r="6" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="54"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="49"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="38"/>
     </row>
     <row r="8" spans="2:11" ht="90" x14ac:dyDescent="0.25">
       <c r="B8" s="15" t="s">
@@ -3703,13 +3705,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="24" x14ac:dyDescent="0.4">
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="40"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="32"/>
     </row>
     <row r="2" spans="2:9" ht="37.5" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
@@ -3720,43 +3722,43 @@
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="42"/>
+      <c r="F2" s="34"/>
     </row>
     <row r="3" spans="2:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
     </row>
     <row r="4" spans="2:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
     </row>
     <row r="5" spans="2:9" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="54"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
     </row>
     <row r="6" spans="2:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="54"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
     </row>
     <row r="8" spans="2:9" ht="56.25" x14ac:dyDescent="0.25">
       <c r="B8" s="15" t="s">
@@ -4067,15 +4069,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="24" x14ac:dyDescent="0.4">
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="41"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="33"/>
     </row>
     <row r="2" spans="2:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
@@ -4087,52 +4089,52 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="43"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="35"/>
     </row>
     <row r="3" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="49"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="38"/>
     </row>
     <row r="4" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="49"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="38"/>
     </row>
     <row r="5" spans="2:11" ht="37.5" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="54"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="49"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="38"/>
     </row>
     <row r="6" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="54"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="49"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="38"/>
     </row>
     <row r="8" spans="2:11" s="1" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="B8" s="17" t="s">
@@ -4338,15 +4340,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="24" x14ac:dyDescent="0.4">
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="41"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="33"/>
     </row>
     <row r="2" spans="2:10" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
@@ -4358,52 +4360,52 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="43"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="35"/>
     </row>
     <row r="3" spans="2:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="49"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="38"/>
     </row>
     <row r="4" spans="2:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="49"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="38"/>
     </row>
     <row r="5" spans="2:10" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="54"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="49"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="38"/>
     </row>
     <row r="6" spans="2:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="54"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="49"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="38"/>
     </row>
     <row r="8" spans="2:10" ht="90" x14ac:dyDescent="0.25">
       <c r="B8" s="15" t="s">
@@ -4595,14 +4597,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="24" x14ac:dyDescent="0.4">
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="41"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="33"/>
     </row>
     <row r="2" spans="2:10" ht="56.25" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
@@ -4613,48 +4615,48 @@
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="43"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="35"/>
     </row>
     <row r="3" spans="2:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="49"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="38"/>
     </row>
     <row r="4" spans="2:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="49"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="38"/>
     </row>
     <row r="5" spans="2:10" ht="56.25" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="54"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="49"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="38"/>
     </row>
     <row r="6" spans="2:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="54"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="49"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="38"/>
     </row>
     <row r="8" spans="2:10" s="9" customFormat="1" ht="162" x14ac:dyDescent="0.25">
       <c r="B8" s="15" t="s">
@@ -4830,26 +4832,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b18f8198-02fb-408b-a649-baf04150ea28">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="0f01b7b4-d4b6-47da-93c5-cffa90a406b9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D80C9320661FCB478F077E19A50F7652" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8169698a23ce641b0e514e4179e9fb48">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0f01b7b4-d4b6-47da-93c5-cffa90a406b9" xmlns:ns3="b18f8198-02fb-408b-a649-baf04150ea28" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2c955a956371819644e2cb74c9337ca9" ns2:_="" ns3:_="">
     <xsd:import namespace="0f01b7b4-d4b6-47da-93c5-cffa90a406b9"/>
@@ -5098,10 +5080,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b18f8198-02fb-408b-a649-baf04150ea28">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0f01b7b4-d4b6-47da-93c5-cffa90a406b9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E88113A-166D-44CD-886E-1102874B4258}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F5E3A78-D3D4-4E16-B9AF-E3B8ACF9F7D8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="0f01b7b4-d4b6-47da-93c5-cffa90a406b9"/>
+    <ds:schemaRef ds:uri="b18f8198-02fb-408b-a649-baf04150ea28"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5118,20 +5131,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F5E3A78-D3D4-4E16-B9AF-E3B8ACF9F7D8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E88113A-166D-44CD-886E-1102874B4258}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="0f01b7b4-d4b6-47da-93c5-cffa90a406b9"/>
-    <ds:schemaRef ds:uri="b18f8198-02fb-408b-a649-baf04150ea28"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>